--- a/xlsx/carteira_mensal/Fev_2026.xlsx
+++ b/xlsx/carteira_mensal/Fev_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="114">
   <si>
     <t>Acompanhamento de Carteira</t>
   </si>
@@ -75,24 +75,24 @@
     <t>Data de Criação do Projeto</t>
   </si>
   <si>
+    <t>/  /     até   /  /</t>
+  </si>
+  <si>
+    <t>Data de Criação do Orçamento</t>
+  </si>
+  <si>
+    <t>/  /     00:00 até   /  /     00:00</t>
+  </si>
+  <si>
+    <t>Data de Criação do Contrato</t>
+  </si>
+  <si>
+    <t>Data de Assinatura do Contrato</t>
+  </si>
+  <si>
     <t>01/02/2026 até 28/02/2026</t>
   </si>
   <si>
-    <t>Data de Criação do Orçamento</t>
-  </si>
-  <si>
-    <t>/  /     00:00 até   /  /     00:00</t>
-  </si>
-  <si>
-    <t>Data de Criação do Contrato</t>
-  </si>
-  <si>
-    <t>/  /     até   /  /</t>
-  </si>
-  <si>
-    <t>Data de Assinatura do Contrato</t>
-  </si>
-  <si>
     <t>Data de Criação do Cliente</t>
   </si>
   <si>
@@ -153,21 +153,51 @@
     <t>Contrato</t>
   </si>
   <si>
+    <t>Krisdany Vinícius Santos de Magalhães Cavalcante</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>15/01/26</t>
+  </si>
+  <si>
+    <t>ROSANGELA PACHECO</t>
+  </si>
+  <si>
+    <t>Orçamento 2</t>
+  </si>
+  <si>
+    <t>11/02/26</t>
+  </si>
+  <si>
+    <t>09/02/26</t>
+  </si>
+  <si>
+    <t>GUILHERME FLORA GRESPAN</t>
+  </si>
+  <si>
+    <t>Já é Cliente</t>
+  </si>
+  <si>
+    <t>23/01/26</t>
+  </si>
+  <si>
+    <t>Orçamento 1</t>
+  </si>
+  <si>
+    <t>18/02/26</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
     <t>Marie hortense levet Hirschfelder</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
     <t>03/02/26</t>
   </si>
   <si>
-    <t>ROSANGELA PACHECO</t>
-  </si>
-  <si>
-    <t>Orçamento 1</t>
-  </si>
-  <si>
     <t>24/02/26</t>
   </si>
   <si>
@@ -177,9 +207,6 @@
     <t>KEYLA CRISTINA CASSARO GUIDONI</t>
   </si>
   <si>
-    <t>Já é Cliente</t>
-  </si>
-  <si>
     <t>ERIC SERPA</t>
   </si>
   <si>
@@ -201,9 +228,6 @@
     <t>2429- JONATHAN APARECIDO DINIZ</t>
   </si>
   <si>
-    <t>11/02/26</t>
-  </si>
-  <si>
     <t>FELIPE DOMINGOS BARBOSA</t>
   </si>
   <si>
@@ -213,12 +237,6 @@
     <t>Gabriela de Freitas Barbosa</t>
   </si>
   <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>18/02/26</t>
-  </si>
-  <si>
     <t>13/02/26</t>
   </si>
   <si>
@@ -282,9 +300,6 @@
     <t>Carina Pereira</t>
   </si>
   <si>
-    <t>Orçamento 2</t>
-  </si>
-  <si>
     <t>Moo Sik Song</t>
   </si>
   <si>
@@ -297,7 +312,7 @@
     <t>Quantidade de Projetos</t>
   </si>
   <si>
-    <t>17</t>
+    <t>19</t>
   </si>
   <si>
     <t>Quantidade de Orçamentos</t>
@@ -312,34 +327,34 @@
     <t>Valor Total Bruto</t>
   </si>
   <si>
-    <t>695.164,69</t>
-  </si>
-  <si>
-    <t>540.024,93</t>
+    <t>796.374,46</t>
+  </si>
+  <si>
+    <t>617.524,93</t>
   </si>
   <si>
     <t>Valor Total Líquido</t>
   </si>
   <si>
-    <t>469.945,90</t>
+    <t>541.894,38</t>
   </si>
   <si>
     <t>Total Líquido sem o Per</t>
   </si>
   <si>
-    <t>464.864,24</t>
+    <t>536.812,72</t>
   </si>
   <si>
     <t>Total Diferença Financeira</t>
   </si>
   <si>
-    <t>70.079,03</t>
+    <t>75.630,55</t>
   </si>
   <si>
     <t>Total Adicional dos Ambientes</t>
   </si>
   <si>
-    <t>22.967,41</t>
+    <t>30.411,10</t>
   </si>
 </sst>
 </file>
@@ -408,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:O58"/>
+  <dimension ref="A2:O60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.22265625" customWidth="true" bestFit="true"/>
@@ -536,15 +551,15 @@
         <v>23</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -552,7 +567,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -560,7 +575,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -666,7 +681,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="n">
-        <v>596.0</v>
+        <v>548.0</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
@@ -675,7 +690,7 @@
         <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G31" t="s">
         <v>50</v>
@@ -684,22 +699,22 @@
         <v>51</v>
       </c>
       <c r="I31" t="n">
-        <v>123000.0</v>
+        <v>67000.0</v>
       </c>
       <c r="J31" t="n">
-        <v>20899.86</v>
+        <v>5551.52</v>
       </c>
       <c r="K31" t="n">
-        <v>102100.14</v>
+        <v>61448.48</v>
       </c>
       <c r="L31" t="n">
-        <v>102100.14</v>
+        <v>61448.48</v>
       </c>
       <c r="M31" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="N31" t="n">
-        <v>59601.0</v>
+        <v>54802.0</v>
       </c>
       <c r="O31" t="s">
         <v>52</v>
@@ -713,69 +728,69 @@
         <v>54</v>
       </c>
       <c r="C32" t="n">
-        <v>595.0</v>
+        <v>571.0</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F32" t="n">
         <v>1.0</v>
       </c>
       <c r="G32" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H32" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="I32" t="n">
-        <v>110.0</v>
+        <v>10500.0</v>
       </c>
       <c r="J32" t="n">
         <v>0.0</v>
       </c>
       <c r="K32" t="n">
-        <v>110.0</v>
+        <v>10500.0</v>
       </c>
       <c r="L32" t="n">
-        <v>110.0</v>
+        <v>10500.0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.04</v>
+        <v>2.0</v>
       </c>
       <c r="N32" t="n">
-        <v>59501.0</v>
+        <v>57101.0</v>
       </c>
       <c r="O32" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
         <v>47</v>
       </c>
       <c r="C33" t="n">
-        <v>594.0</v>
+        <v>596.0</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E33" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F33" t="n">
         <v>1.0</v>
       </c>
       <c r="G33" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H33" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I33" t="n">
         <v>123000.0</v>
@@ -790,57 +805,57 @@
         <v>102100.14</v>
       </c>
       <c r="M33" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="N33" t="n">
-        <v>59401.0</v>
+        <v>59601.0</v>
       </c>
       <c r="O33" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C34" t="n">
-        <v>599.0</v>
+        <v>595.0</v>
       </c>
       <c r="D34" t="s">
         <v>60</v>
       </c>
       <c r="E34" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F34" t="n">
         <v>1.0</v>
       </c>
       <c r="G34" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H34" t="s">
         <v>60</v>
       </c>
       <c r="I34" t="n">
-        <v>282.0</v>
+        <v>110.0</v>
       </c>
       <c r="J34" t="n">
         <v>0.0</v>
       </c>
       <c r="K34" t="n">
-        <v>282.0</v>
+        <v>110.0</v>
       </c>
       <c r="L34" t="n">
-        <v>282.0</v>
+        <v>110.0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.0</v>
+        <v>2.04</v>
       </c>
       <c r="N34" t="n">
-        <v>59901.0</v>
+        <v>59501.0</v>
       </c>
       <c r="O34" t="s">
         <v>60</v>
@@ -848,143 +863,143 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C35" t="n">
-        <v>610.0</v>
+        <v>594.0</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E35" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F35" t="n">
         <v>1.0</v>
       </c>
       <c r="G35" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H35" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I35" t="n">
-        <v>2500.0</v>
+        <v>123000.0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0</v>
+        <v>20899.86</v>
       </c>
       <c r="K35" t="n">
-        <v>2500.0</v>
+        <v>102100.14</v>
       </c>
       <c r="L35" t="n">
-        <v>2500.0</v>
+        <v>102100.14</v>
       </c>
       <c r="M35" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="N35" t="n">
-        <v>61001.0</v>
+        <v>59401.0</v>
       </c>
       <c r="O35" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" t="n">
+        <v>599.0</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" t="s">
         <v>65</v>
-      </c>
-      <c r="B36" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" t="n">
-        <v>614.0</v>
-      </c>
-      <c r="D36" t="s">
-        <v>66</v>
-      </c>
-      <c r="E36" t="s">
-        <v>55</v>
       </c>
       <c r="F36" t="n">
         <v>1.0</v>
       </c>
       <c r="G36" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H36" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I36" t="n">
-        <v>16000.0</v>
+        <v>282.0</v>
       </c>
       <c r="J36" t="n">
-        <v>440.31</v>
+        <v>0.0</v>
       </c>
       <c r="K36" t="n">
-        <v>15559.69</v>
+        <v>282.0</v>
       </c>
       <c r="L36" t="n">
-        <v>15559.69</v>
+        <v>282.0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.11</v>
+        <v>3.0</v>
       </c>
       <c r="N36" t="n">
-        <v>61401.0</v>
+        <v>59901.0</v>
       </c>
       <c r="O36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C37" t="n">
-        <v>619.0</v>
+        <v>610.0</v>
       </c>
       <c r="D37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" t="s">
         <v>71</v>
-      </c>
-      <c r="E37" t="s">
-        <v>55</v>
       </c>
       <c r="F37" t="n">
         <v>1.0</v>
       </c>
       <c r="G37" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H37" t="s">
         <v>72</v>
       </c>
       <c r="I37" t="n">
-        <v>32896.0</v>
+        <v>2500.0</v>
       </c>
       <c r="J37" t="n">
-        <v>3446.57</v>
+        <v>0.0</v>
       </c>
       <c r="K37" t="n">
-        <v>29449.43</v>
+        <v>2500.0</v>
       </c>
       <c r="L37" t="n">
-        <v>29449.43</v>
+        <v>2500.0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="N37" t="n">
-        <v>61901.0</v>
+        <v>61001.0</v>
       </c>
       <c r="O37" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
@@ -995,43 +1010,43 @@
         <v>54</v>
       </c>
       <c r="C38" t="n">
-        <v>623.0</v>
+        <v>614.0</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F38" t="n">
         <v>1.0</v>
       </c>
       <c r="G38" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H38" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I38" t="n">
-        <v>35656.92</v>
+        <v>16000.0</v>
       </c>
       <c r="J38" t="n">
-        <v>4117.37</v>
+        <v>440.31</v>
       </c>
       <c r="K38" t="n">
-        <v>31539.55</v>
+        <v>15559.69</v>
       </c>
       <c r="L38" t="n">
-        <v>28552.92</v>
+        <v>15559.69</v>
       </c>
       <c r="M38" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="N38" t="n">
-        <v>62301.0</v>
+        <v>61401.0</v>
       </c>
       <c r="O38" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39">
@@ -1039,375 +1054,375 @@
         <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C39" t="n">
-        <v>629.0</v>
+        <v>619.0</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F39" t="n">
         <v>1.0</v>
       </c>
       <c r="G39" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H39" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I39" t="n">
-        <v>41200.0</v>
+        <v>32896.0</v>
       </c>
       <c r="J39" t="n">
-        <v>3563.42</v>
+        <v>3446.57</v>
       </c>
       <c r="K39" t="n">
-        <v>37636.58</v>
+        <v>29449.43</v>
       </c>
       <c r="L39" t="n">
-        <v>37636.58</v>
+        <v>29449.43</v>
       </c>
       <c r="M39" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="N39" t="n">
-        <v>62901.0</v>
+        <v>61901.0</v>
       </c>
       <c r="O39" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C40" t="n">
-        <v>628.0</v>
+        <v>623.0</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E40" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>
       </c>
       <c r="G40" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H40" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="I40" t="n">
-        <v>31837.03</v>
+        <v>35656.92</v>
       </c>
       <c r="J40" t="n">
-        <v>8516.72</v>
+        <v>4117.37</v>
       </c>
       <c r="K40" t="n">
-        <v>23320.31</v>
+        <v>31539.55</v>
       </c>
       <c r="L40" t="n">
-        <v>22758.65</v>
+        <v>28552.92</v>
       </c>
       <c r="M40" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="N40" t="n">
-        <v>62801.0</v>
+        <v>62301.0</v>
       </c>
       <c r="O40" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C41" t="n">
-        <v>635.0</v>
+        <v>629.0</v>
       </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>
       </c>
       <c r="G41" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I41" t="n">
-        <v>67000.0</v>
+        <v>41200.0</v>
       </c>
       <c r="J41" t="n">
-        <v>3645.83</v>
+        <v>3563.42</v>
       </c>
       <c r="K41" t="n">
-        <v>63354.17</v>
+        <v>37636.58</v>
       </c>
       <c r="L41" t="n">
-        <v>61820.8</v>
+        <v>37636.58</v>
       </c>
       <c r="M41" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="N41" t="n">
-        <v>63501.0</v>
+        <v>62901.0</v>
       </c>
       <c r="O41" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C42" t="n">
-        <v>634.0</v>
+        <v>628.0</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="E42" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F42" t="n">
         <v>1.0</v>
       </c>
       <c r="G42" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H42" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="I42" t="n">
-        <v>6534.13</v>
+        <v>31837.03</v>
       </c>
       <c r="J42" t="n">
-        <v>618.76</v>
+        <v>8516.72</v>
       </c>
       <c r="K42" t="n">
-        <v>5915.37</v>
+        <v>23320.31</v>
       </c>
       <c r="L42" t="n">
-        <v>5915.37</v>
+        <v>22758.65</v>
       </c>
       <c r="M42" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="N42" t="n">
-        <v>63401.0</v>
+        <v>62801.0</v>
       </c>
       <c r="O42" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C43" t="n">
-        <v>639.0</v>
+        <v>635.0</v>
       </c>
       <c r="D43" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="E43" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F43" t="n">
         <v>1.0</v>
       </c>
       <c r="G43" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H43" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I43" t="n">
-        <v>32000.0</v>
+        <v>67000.0</v>
       </c>
       <c r="J43" t="n">
-        <v>2767.7</v>
+        <v>3645.83</v>
       </c>
       <c r="K43" t="n">
-        <v>29232.3</v>
+        <v>63354.17</v>
       </c>
       <c r="L43" t="n">
-        <v>29232.3</v>
+        <v>61820.8</v>
       </c>
       <c r="M43" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="N43" t="n">
-        <v>63901.0</v>
+        <v>63501.0</v>
       </c>
       <c r="O43" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C44" t="n">
-        <v>638.0</v>
+        <v>634.0</v>
       </c>
       <c r="D44" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="E44" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>
       </c>
       <c r="G44" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H44" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="I44" t="n">
-        <v>1149.0</v>
+        <v>6534.13</v>
       </c>
       <c r="J44" t="n">
-        <v>28.57</v>
+        <v>618.76</v>
       </c>
       <c r="K44" t="n">
-        <v>1120.43</v>
+        <v>5915.37</v>
       </c>
       <c r="L44" t="n">
-        <v>1120.43</v>
+        <v>5915.37</v>
       </c>
       <c r="M44" t="n">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
       <c r="N44" t="n">
-        <v>63801.0</v>
+        <v>63401.0</v>
       </c>
       <c r="O44" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C45" t="n">
-        <v>640.0</v>
+        <v>639.0</v>
       </c>
       <c r="D45" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E45" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="F45" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G45" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="H45" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I45" t="n">
-        <v>359.85</v>
+        <v>32000.0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0</v>
+        <v>2767.7</v>
       </c>
       <c r="K45" t="n">
-        <v>359.85</v>
+        <v>29232.3</v>
       </c>
       <c r="L45" t="n">
-        <v>359.85</v>
+        <v>29232.3</v>
       </c>
       <c r="M45" t="n">
-        <v>1.18</v>
+        <v>1.97</v>
       </c>
       <c r="N45" t="n">
-        <v>64002.0</v>
+        <v>63901.0</v>
       </c>
       <c r="O45" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" t="s">
+        <v>76</v>
+      </c>
+      <c r="C46" t="n">
+        <v>638.0</v>
+      </c>
+      <c r="D46" t="s">
         <v>90</v>
       </c>
-      <c r="B46" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" t="n">
-        <v>644.0</v>
-      </c>
-      <c r="D46" t="s">
-        <v>77</v>
-      </c>
       <c r="E46" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F46" t="n">
         <v>1.0</v>
       </c>
       <c r="G46" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H46" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I46" t="n">
-        <v>7800.0</v>
+        <v>1149.0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0</v>
+        <v>28.57</v>
       </c>
       <c r="K46" t="n">
-        <v>7800.0</v>
+        <v>1120.43</v>
       </c>
       <c r="L46" t="n">
-        <v>7800.0</v>
+        <v>1120.43</v>
       </c>
       <c r="M46" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="N46" t="n">
-        <v>64401.0</v>
+        <v>63801.0</v>
       </c>
       <c r="O46" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47">
@@ -1415,75 +1430,153 @@
         <v>92</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C47" t="n">
-        <v>649.0</v>
+        <v>640.0</v>
       </c>
       <c r="D47" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="F47" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G47" t="s">
         <v>50</v>
       </c>
       <c r="H47" t="s">
+        <v>83</v>
+      </c>
+      <c r="I47" t="n">
+        <v>359.85</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>359.85</v>
+      </c>
+      <c r="L47" t="n">
+        <v>359.85</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N47" t="n">
+        <v>64002.0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" t="n">
+        <v>644.0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" t="s">
+        <v>49</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G48" t="s">
+        <v>56</v>
+      </c>
+      <c r="H48" t="s">
+        <v>83</v>
+      </c>
+      <c r="I48" t="n">
+        <v>7800.0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>7800.0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>7800.0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="N48" t="n">
+        <v>64401.0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" t="s">
         <v>76</v>
       </c>
-      <c r="I47" t="n">
+      <c r="C49" t="n">
+        <v>649.0</v>
+      </c>
+      <c r="D49" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>56</v>
+      </c>
+      <c r="H49" t="s">
+        <v>82</v>
+      </c>
+      <c r="I49" t="n">
         <v>18700.0</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J49" t="n">
         <v>1134.06</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K49" t="n">
         <v>17565.94</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L49" t="n">
         <v>17565.94</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M49" t="n">
         <v>1.95</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N49" t="n">
         <v>64901.0</v>
       </c>
-      <c r="O47" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>94</v>
+      <c r="O49" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>99</v>
@@ -1491,42 +1584,58 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/carteira_mensal/Fev_2026.xlsx
+++ b/xlsx/carteira_mensal/Fev_2026.xlsx
@@ -210,7 +210,7 @@
     <t>ERIC SERPA</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
+    <t>bianca rodrigues</t>
   </si>
   <si>
     <t>20/02/26</t>
